--- a/stories/arbres/ATOM-TMP.JOU.001-04.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le jour, Ulysse joue au jardin avec maman. Le soleil brille. Il fait chaud. Maman dit : le jour, c'est le soleil. Ulysse sent la chaleur sur les mains. Le soir arrive. Le ciel devient bleu foncé. Ulysse voit la lune. Il voit les étoiles. Papa dit : la nuit, c'est la lune. Ulysse met son pyjama. Papa dit : la nuit, on fait dodo. Ulysse se couche. Le lendemain, le soleil revient. Ulysse joue encore au jardin. Le soir, la lune revient. Ulysse se souvient. Il dit : dodo la nuit. Même leçon, autre jour. Le jour le soleil. La nuit la lune. Dodo la nuit.</t>
+          <t>Le jour, Ulysse joue au jardin avec maman. Le soleil brille. Il fait chaud. Le jour, c'est le soleil. Ulysse sent la chaleur sur les mains. Le soir arrive. Le ciel devient bleu foncé. Ulysse voit la lune. Il voit les étoiles. La nuit, c'est la lune. Ulysse met son pyjama. La nuit, on fait dodo. Ulysse se couche. Le lendemain, le soleil revient. Ulysse joue encore au jardin. Le soir, la lune revient. Ulysse se souvient. Dodo la nuit. Même leçon, autre jour. Le jour le soleil. La nuit la lune. Dodo la nuit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le jour, Ulysse joue au jardin avec maman. Le soleil brille. Il fait chaud.
+maman|Le jour, c'est le soleil.
+narrateur|Ulysse sent la chaleur sur les mains. Le soir arrive. Le ciel devient bleu foncé. Ulysse voit la lune. Il voit les étoiles.
+papa|La nuit, c'est la lune.
+narrateur|Ulysse met son pyjama.
+papa|La nuit, on fait dodo.
+narrateur|Ulysse se couche. Le lendemain, le soleil revient. Ulysse joue encore au jardin. Le soir, la lune revient. Ulysse se souvient.
+narrateur|Dodo la nuit. Même leçon, autre jour.
+narrateur|Le jour le soleil. La nuit la lune. Dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1498,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|La lune est là. Quel moment est-ce ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Ulysse a vu le soleil le jour. Il a vu la lune la nuit. Il fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1838,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa baisse la lumière. Ulysse respire.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2005,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2045,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.JOU.001-04.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,7 @@
 narrateur|Le jour le soleil. La nuit la lune. Dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1505,6 +1511,7 @@
           <t>narrateur|La lune est là. Quel moment est-ce ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1683,7 @@
           <t>narrateur|Ulysse a vu le soleil le jour. Il a vu la lune la nuit. Il fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1843,6 +1851,7 @@
           <t>narrateur|Papa baisse la lumière. Ulysse respire.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2010,6 +2019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2028,7 +2038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2052,6 +2062,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2253,6 +2277,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.JOU.001-04.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ulysse voit le soleil puis la lune</t>
+          <t>Les chaussettes de Raphaël</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël veut le goûter sur la crête. Un ruisseau mouille ses chaussettes. Elles sèchent au soleil. Le soir, la lune tient la crête, les chaussettes sont sèches.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le jour, Ulysse joue au jardin avec maman. Le soleil brille. Il fait chaud. Le jour, c'est le soleil. Ulysse sent la chaleur sur les mains. Le soir arrive. Le ciel devient bleu foncé. Ulysse voit la lune. Il voit les étoiles. La nuit, c'est la lune. Ulysse met son pyjama. La nuit, on fait dodo. Ulysse se couche. Le lendemain, le soleil revient. Ulysse joue encore au jardin. Le soir, la lune revient. Ulysse se souvient. Dodo la nuit. Même leçon, autre jour. Le jour le soleil. La nuit la lune. Dodo la nuit.</t>
+          <t>L'air de la crête pique les oreilles. L'herbe est rase, un peu grise. Une pierre tient encore le froid de la nuit. Ça sent le thym et la laine. Tu as senti le vent, Raphaël ? Il pique. Oui. Plus haut, il pique davantage. Je veux le goûter, là haut. Sur la crête ? Oui. En ce moment, Raphaël saute le ruisseau. L'eau est étroite, mais vive. Une chaussette prend une goutte, puis l'autre. Elles sont mouillées. On les ôte ? On les met au soleil. Le soleil tient déjà la crête, nette. La pierre devient tiède, puis chaude. Maman étend les chaussettes sur la pierre. Elles font deux virgules sombres, qui s'éclaircissent. Elles sèchent ? Le jour les sèche. Le soleil est sur la crête. Raphaël marche pieds nus, l'herbe pique. Papa ouvre le sac du goûter. Le pain sent encore la maison. Le fromage. Le voilà. Ils mangent face à la ligne claire. Un nuage passe, l'ombre court sur la pierre. Mes chaussettes. Elles sont encore un peu froides. Encore un peu de jour. Plus tard, le vent tourne, plus doux. Le ciel se creuse, bleu foncé. Une lune ronde s'accroche à la crête. Elle est sur la pierre. La nuit est là. La lune est sur la crête. On rentre au chalet ? Les chaussettes. Elles sont sèches, un peu raides. Merci, soleil. Merci, Raphaël. Tu as attendu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le jour, Ulysse joue au jardin avec maman. Le &lt;emphasis level="moderate"&gt;soleil&lt;/emphasis&gt; brille. Il fait chaud. Maman dit : le jour, c'est le soleil. Ulysse sent la chaleur sur les mains. Le soir arrive. Le ciel devient bleu foncé. Ulysse voit la lune. Il voit les étoiles. Papa dit : la nuit, c'est la lune. Ulysse met son pyjama. Papa dit : la nuit, on fait dodo. Ulysse se couche. Le lendemain, le soleil revient. Ulysse joue encore au jardin. Le soir, la lune revient. Ulysse se souvient. Il dit : dodo la nuit. Même leçon, autre jour. Le jour le soleil. La nuit la lune. Dodo la nuit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'air de la crête pique les oreilles. L'herbe est rase, un peu grise. Une pierre tient encore le froid de la nuit. Ça sent le thym et la laine. Tu as senti le vent, Raphaël ? Il pique. Oui. Plus haut, il pique davantage. Je veux le goûter, là haut. Sur la crête ? Oui. En ce moment, Raphaël saute le ruisseau. L'eau est étroite, mais vive. Une chaussette prend une goutte, puis l'autre. Elles sont mouillées. On les ôte ? On les met au soleil. Le soleil tient déjà la crête, nette. La pierre devient tiède, puis chaude. Maman étend les chaussettes sur la pierre. Elles font deux virgules sombres, qui s'éclaircissent. Elles sèchent ? Le jour les sèche. Le soleil est sur la crête. Raphaël marche pieds nus, l'herbe pique. Papa ouvre le sac du goûter. Le pain sent encore la maison. Le fromage. Le voilà. Ils mangent face à la ligne claire. Un nuage passe, l'ombre court sur la pierre. Mes chaussettes. Elles sont encore un peu froides. Encore un peu de jour. Plus tard, le vent tourne, plus doux. Le ciel se creuse, bleu foncé. Une lune ronde s'accroche à la crête. Elle est sur la pierre. La nuit est là. La lune est sur la crête. On rentre au chalet ? Les chaussettes. Elles sont sèches, un peu raides. Merci, soleil. Merci, Raphaël. Tu as attendu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,18 +1324,59 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le jour, Ulysse joue au jardin avec maman. Le soleil brille. Il fait chaud.
-maman|Le jour, c'est le soleil.
-narrateur|Ulysse sent la chaleur sur les mains. Le soir arrive. Le ciel devient bleu foncé. Ulysse voit la lune. Il voit les étoiles.
-papa|La nuit, c'est la lune.
-narrateur|Ulysse met son pyjama.
-papa|La nuit, on fait dodo.
-narrateur|Ulysse se couche. Le lendemain, le soleil revient. Ulysse joue encore au jardin. Le soir, la lune revient. Ulysse se souvient.
-narrateur|Dodo la nuit. Même leçon, autre jour.
-narrateur|Le jour le soleil. La nuit la lune. Dodo la nuit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|L'air de la crête pique les oreilles.
+narrateur|L'herbe est rase, un peu grise.
+narrateur|Une pierre tient encore le froid de la nuit.
+narrateur|Ça sent le thym et la laine.
+papa|Tu as senti le vent, Raphaël ?
+enfant-m|Il pique.
+maman|Oui.
+maman|Plus haut, il pique davantage.
+enfant-m|Je veux le goûter, là haut.
+papa|Sur la crête ?
+enfant-m|Oui.
+narrateur|En ce moment, Raphaël saute le ruisseau.
+narrateur|L'eau est étroite, mais vive.
+narrateur|Une chaussette prend une goutte, puis l'autre.
+enfant-m|Elles sont mouillées.
+maman|On les ôte ?
+papa|On les met au soleil.
+narrateur|Le soleil tient déjà la crête, nette.
+narrateur|La pierre devient tiède, puis chaude.
+narrateur|Maman étend les chaussettes sur la pierre.
+narrateur|Elles font deux virgules sombres, qui s'éclaircissent.
+enfant-m|Elles sèchent ?
+papa|Le jour les sèche.
+papa|Le soleil est sur la crête.
+narrateur|Raphaël marche pieds nus, l'herbe pique.
+narrateur|Papa ouvre le sac du goûter.
+narrateur|Le pain sent encore la maison.
+enfant-m|Le fromage.
+maman|Le voilà.
+narrateur|Ils mangent face à la ligne claire.
+narrateur|Un nuage passe, l'ombre court sur la pierre.
+enfant-m|Mes chaussettes.
+papa|Elles sont encore un peu froides.
+maman|Encore un peu de jour.
+narrateur|Plus tard, le vent tourne, plus doux.
+narrateur|Le ciel se creuse, bleu foncé.
+narrateur|Une lune ronde s'accroche à la crête.
+enfant-m|Elle est sur la pierre.
+maman|La nuit est là.
+papa|La lune est sur la crête.
+maman|On rentre au chalet ?
+enfant-m|Les chaussettes.
+narrateur|Elles sont sèches, un peu raides.
+papa|Merci, soleil.
+maman|Merci, Raphaël.
+maman|Tu as attendu.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>vent</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1348,12 +1401,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>La lune est là. Quel moment est-ce ?</t>
+          <t>La lune est sur la crête. Quel moment est-ce ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;lune&lt;/emphasis&gt; est là. Quel moment est-ce ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La lune est sur la crête. Quel moment est-ce ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1368,7 +1421,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>nuit | la nuit | lune | le soir</t>
+          <t>nuit | la nuit | le soir | dodo | c'est la nuit</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1383,7 +1436,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>La lune vient la nuit. Quel moment ?</t>
+          <t>La lune est sur la crête. C'est le jour, ou la nuit ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1425,14 +1478,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1508,10 +1561,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|La lune est là. Quel moment est-ce ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|La lune est sur la crête.
+narrateur|Quel moment est-ce ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1536,12 +1589,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ulysse a vu le soleil le jour. Il a vu la lune la nuit. Il fait dodo la nuit.</t>
+          <t>Raphaël a mangé au soleil, les chaussettes sur la pierre. Maintenant la lune tient la même ligne. Le jour, c'était le soleil. La nuit, c'est la lune. Mes chaussettes sont sèches. Oui. On se couche au chalet ? Encore la lune. On la verra à la fenêtre. Le thym sent encore, dans la laine.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ulysse a vu le &lt;emphasis level="moderate"&gt;soleil&lt;/emphasis&gt; le jour. Il a vu la lune la nuit. Il fait dodo la nuit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a mangé au soleil, les chaussettes sur la pierre. Maintenant la lune tient la même ligne. Le jour, c'était le soleil. La nuit, c'est la lune. Mes chaussettes sont sèches. Oui. On se couche au chalet ? Encore la lune. On la verra à la fenêtre. Le thym sent encore, dans la laine.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1604,7 +1657,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1733,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Ulysse a vu le soleil le jour. Il a vu la lune la nuit. Il fait dodo la nuit.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Raphaël a mangé au soleil, les chaussettes sur la pierre.
+narrateur|Maintenant la lune tient la même ligne.
+papa|Le jour, c'était le soleil.
+maman|La nuit, c'est la lune.
+enfant-m|Mes chaussettes sont sèches.
+papa|Oui.
+papa|On se couche au chalet ?
+enfant-m|Encore la lune.
+maman|On la verra à la fenêtre.
+narrateur|Le thym sent encore, dans la laine.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1708,12 +1769,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa baisse la lumière. Ulysse respire.</t>
+          <t>Le chalet sent le bois chaud. Raphaël enfile les chaussettes, sèches et rêche. Elles chatouillent. Le soleil les a tenues. La nuit, on fait dodo. Tu fermes les yeux ? Je regarde la crête. À la fenêtre, la lune est encore nette. La pierre du goûter n'est plus qu'une ombre. Elle est toujours là. Oui. Papa baisse la lampe. Raphaël respire le thym sur ses chaussettes.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa bais&lt;emphasis level="moderate"&gt;se&lt;/emphasis&gt; la lumière. Ulysse respire.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le chalet sent le bois chaud. Raphaël enfile les chaussettes, sèches et rêche. Elles chatouillent. Le soleil les a tenues. La nuit, on fait dodo. Tu fermes les yeux ? Je regarde la crête. À la fenêtre, la lune est encore nette. La pierre du goûter n'est plus qu'une ombre. Elle est toujours là. Oui. Papa baisse la lampe. Raphaël respire le thym sur ses chaussettes.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1776,7 +1837,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1848,10 +1909,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa baisse la lumière. Ulysse respire.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le chalet sent le bois chaud.
+narrateur|Raphaël enfile les chaussettes, sèches et rêche.
+enfant-m|Elles chatouillent.
+maman|Le soleil les a tenues.
+papa|La nuit, on fait dodo.
+papa|Tu fermes les yeux ?
+enfant-m|Je regarde la crête.
+narrateur|À la fenêtre, la lune est encore nette.
+narrateur|La pierre du goûter n'est plus qu'une ombre.
+maman|Elle est toujours là.
+papa|Oui.
+narrateur|Papa baisse la lampe.
+narrateur|Raphaël respire le thym sur ses chaussettes.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1876,12 +1948,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Les deux chaussettes font deux virgules claires. La lune tient encore la crête. Elles sont sèches. Oui. Le jour les a séchées. Raphaël ferme les yeux, le vent aux oreilles.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les deux chaussettes font deux virgules claires. La lune tient encore la crête. Elles sont sèches. Oui. Le jour les a séchées. Raphaël ferme les yeux, le vent aux oreilles.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1944,7 +2016,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2016,10 +2088,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Les deux chaussettes font deux virgules claires.
+narrateur|La lune tient encore la crête.
+enfant-m|Elles sont sèches.
+maman|Oui.
+papa|Le jour les a séchées.
+narrateur|Raphaël ferme les yeux, le vent aux oreilles.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2038,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2076,6 +2152,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.JOU.001-04.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin puis chambre, deux jours</t>
+          <t>montagne, crête, chalet</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ulysse, maman, papa</t>
+          <t>Raphaël, maman, papa</t>
         </is>
       </c>
     </row>
